--- a/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:50</t>
+          <t>2026-09-29 01:01:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:52</t>
+          <t>2026-09-29 01:01:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 00:53:53</t>
+          <t>2026-09-29 01:01:46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:43</t>
+          <t>2026-09-29 01:40:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:45</t>
+          <t>2026-09-29 01:40:37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:01:46</t>
+          <t>2026-09-29 01:40:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+2.16%1185</t>
+          <t>-1.69%1165</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1185</v>
+        <v>1165</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.72%1,720,000</t>
+          <t>7.75%1,720,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.72%</t>
+          <t>7.75%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.93%5285</t>
+          <t>-0.36%6895</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5285</v>
+        <v>6895</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.89%344,000</t>
+          <t>6.94%260,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.94%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>344000</v>
+        <v>260000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.67%8525</t>
+          <t>-7.1%4910</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8525</v>
+        <v>4910</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.88%213,000</t>
+          <t>6.54%344,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.88%</t>
+          <t>6.54%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>213000</v>
+        <v>344000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+7.96%6920</t>
+          <t>-7.04%7925</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+7.96%</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6920</v>
+        <v>7925</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.82%260,000</t>
+          <t>6.53%213,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.82%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>260000</v>
+        <v>213000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.65%5415</t>
+          <t>-4.25%5185</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.65%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5415</v>
+        <v>5185</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.63%323,000</t>
+          <t>6.48%323,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.63%</t>
+          <t>6.48%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0%2340</t>
+          <t>+4.49%2445</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.49%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2340</v>
+        <v>2445</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.90%665,000</t>
+          <t>6.29%665,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.90%</t>
+          <t>6.29%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.45%3555</t>
+          <t>-4.36%3400</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3555</v>
+        <v>3400</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.09%378,000</t>
+          <t>4.97%378,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.07%1105</t>
+          <t>+1.36%1120</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.72%1,127,000</t>
+          <t>4.88%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.69%2530</t>
+          <t>-0.59%2515</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.69%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2530</v>
+        <v>2515</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.23%441,000</t>
+          <t>4.29%441,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.29%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.19%19835</t>
+          <t>-2.22%19395</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19835</v>
+        <v>19395</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.6%5050</t>
+          <t>-2.57%4920</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.06%212,000</t>
+          <t>4.04%212,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.61%993</t>
+          <t>-4.49%1810</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>993</v>
+        <v>1810</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.87%1,030,000</t>
+          <t>3.71%529,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.71%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1030000</v>
+        <v>529000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.26%1895</t>
+          <t>-6.45%929</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-6.45%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1895</v>
+        <v>929</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.80%529,000</t>
+          <t>3.70%1,030,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>529000</v>
+        <v>1030000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.48%1240</t>
+          <t>+2.42%1270</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+2.42%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1240</v>
+        <v>1270</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.47%739,000</t>
+          <t>3.63%739,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.47%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:35</t>
+          <t>2026-09-29 22:56:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.75%3310</t>
+          <t>-5.14%3140</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3310</v>
+        <v>3140</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.07%245,000</t>
+          <t>2.98%245,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.1%5670</t>
+          <t>-1.5%5585</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5670</v>
+        <v>5585</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.58%120,000</t>
+          <t>2.59%120,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.32%12350</t>
+          <t>-1.9%12115</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>12350</v>
+        <v>12115</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>-0.67%1485</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.73%306,000</t>
+          <t>1.76%306,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1%2475</t>
+          <t>+3.59%1585</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>+3.59%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2475</v>
+        <v>1585</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.68%179,000</t>
+          <t>1.73%282,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>179000</v>
+        <v>282000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.65%1530</t>
+          <t>0%2475</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1530</v>
+        <v>2475</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.63%282,000</t>
+          <t>1.71%179,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>282000</v>
+        <v>179000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.35%513</t>
+          <t>+2.34%525</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>+2.34%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.26%650,000</t>
+          <t>1.32%650,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7734印能科技</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+6.59%2750</t>
+          <t>+1.89%216</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+6.59%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2750</v>
+        <v>216</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.15%110,000</t>
+          <t>1.17%1,400,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>110000</v>
+        <v>1400000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>7734印能科技</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.44%212</t>
+          <t>-2.55%2680</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>212</v>
+        <v>2680</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.12%1,400,000</t>
+          <t>1.14%110,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1400000</v>
+        <v>110000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.75%154</t>
+          <t>-0.32%153.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>154</v>
+        <v>153.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.04%1,778,000</t>
+          <t>1.06%1,778,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.48%2115</t>
+          <t>-0.71%2100</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2115</v>
+        <v>2100</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.79%99,139</t>
+          <t>0.81%99,139</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.53%1910</t>
+          <t>+9.62%1310</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+9.62%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1910</v>
+        <v>1310</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.68%94,000</t>
+          <t>0.75%148,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>94000</v>
+        <v>148000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,25 +2090,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.83%1195</t>
+          <t>-3.93%1835</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1195</v>
+        <v>1835</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.67%148,000</t>
+          <t>0.67%94,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>148000</v>
+        <v>94000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.42%5850</t>
+          <t>-2.99%5675</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5850</v>
+        <v>5675</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.4%497.5</t>
+          <t>-1.11%492</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>497.5</v>
+        <v>492</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.47%250,000</t>
+          <t>0.48%250,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:37</t>
+          <t>2026-09-29 22:56:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0%840</t>
+          <t>-3.1%814</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.21%948</t>
+          <t>-0.32%945</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+3.48%238</t>
+          <t>-2.31%232.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+3.48%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>238</v>
+        <v>232.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.28%728</t>
+          <t>+4.95%764</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+4.95%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>728</v>
+        <v>764</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.26%95,000</t>
+          <t>0.28%95,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.45%170.5</t>
+          <t>+4.69%178.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>170.5</v>
+        <v>178.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.14%211,000</t>
+          <t>0.15%211,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.67%225</t>
+          <t>+7.11%241</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+7.11%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.06%72,000</t>
+          <t>0.07%72,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+2.3%311</t>
+          <t>-5.31%294.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>311</v>
+        <v>294.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.38%246</t>
+          <t>-1.83%241.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-1.83%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>246</v>
+        <v>241.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.42%480</t>
+          <t>0%480</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.27%3770</t>
+          <t>-2.25%3685</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.27%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3770</v>
+        <v>3685</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+3%722</t>
+          <t>+1.11%730</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.87%699</t>
+          <t>-1.72%687</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.94%183.5</t>
+          <t>-0.54%182.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>183.5</v>
+        <v>182.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%1690</t>
+          <t>+1.18%1710</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1690</v>
+        <v>1710</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.64%1555</t>
+          <t>-2.89%1510</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1555</v>
+        <v>1510</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 01:40:38</t>
+          <t>2026-09-29 22:56:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.63%1210</t>
+          <t>0%1210</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">

--- a/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:09</t>
+          <t>2026-09-29 23:07:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:10</t>
+          <t>2026-09-29 23:07:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 22:56:11</t>
+          <t>2026-09-29 23:07:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-29_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:08</t>
+          <t>2026-09-29 23:52:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:09</t>
+          <t>2026-09-29 23:52:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-29 23:07:10</t>
+          <t>2026-09-29 23:52:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
